--- a/artfynd/A 32795-2025 artfynd.xlsx
+++ b/artfynd/A 32795-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88627727</v>
+        <v>88627690</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532842.0330290146</v>
+        <v>532772</v>
       </c>
       <c r="R2" t="n">
-        <v>7105845.787046508</v>
+        <v>7105585</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,12 +783,7 @@
         <v>88627714</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532799.1256826696</v>
+        <v>532799</v>
       </c>
       <c r="R3" t="n">
-        <v>7105634.825925462</v>
+        <v>7105635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88627690</v>
+        <v>88627727</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532772.0421116207</v>
+        <v>532842</v>
       </c>
       <c r="R4" t="n">
-        <v>7105585.084076548</v>
+        <v>7105846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +956,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,37 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88627684</v>
+        <v>88627731</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532709.1170217578</v>
+        <v>532895</v>
       </c>
       <c r="R5" t="n">
-        <v>7105443.051147276</v>
+        <v>7105877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1061,9 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,6 +1088,111 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88627684</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ursvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532709</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7105443</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-10-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-10-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 32795-2025 artfynd.xlsx
+++ b/artfynd/A 32795-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88627690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88627714</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88627727</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88627731</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88627684</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>